--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B153607-8F59-41EB-89B9-FDF7F48F8906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3516" yWindow="3960" windowWidth="21600" windowHeight="11508" tabRatio="860" firstSheet="6" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="860" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="133">
   <si>
     <t>對話內容</t>
   </si>
@@ -85,33 +86,18 @@
     <t>？？？？？</t>
   </si>
   <si>
-    <t>來自17、18歲年輕女性，靦腆中又帶著敬重的語調，並非透過訊號傳遞，而是透過空氣中的震動，切實的扣嚮耳膜。</t>
-  </si>
-  <si>
     <t>您的臉色好差，博士？露易絲？您有聽見我嗎？</t>
   </si>
   <si>
-    <t>露易絲的嘴角抽搐了一剎，很快又歸於平靜。</t>
-  </si>
-  <si>
     <t>你在找我？有什麼事嗎？</t>
   </si>
   <si>
-    <t>垂掛在充當脖頸處的曲折，是露易絲在企業最熟悉不過的物件──工牌。</t>
-  </si>
-  <si>
-    <t>助理：克拉拉。</t>
-  </si>
-  <si>
     <t>是的！</t>
   </si>
   <si>
     <t>通訊器修好後，我們有陸續聯絡上社區裡的其他人了。</t>
   </si>
   <si>
-    <t>(......社區，在我來到這裡之後他們不只一次提過，雖然現在看不出來，但這裡以前是小有規模的聚落嗎？)</t>
-  </si>
-  <si>
     <t>已經有客人向我們回電，談好要來的時間，但我們現在人手不足，才勉強恢復到可以營業的狀態......</t>
   </si>
   <si>
@@ -127,12 +113,6 @@
     <t>......加上通訊器也因為襲擊損壞，你們與以前的居民也失聯了，是嗎？</t>
   </si>
   <si>
-    <t>克拉拉頷首表示推理正確。露易絲不確定在襲擊事件發生後，她究竟走了多遠才抵達現在的落腳處，但14個日落的路程評估也是不少的距離。</t>
-  </si>
-  <si>
-    <t>——襲擊事件的範圍比預想的大上不少，並不是特別針對他們外來者的攻擊，而是自然災害？</t>
-  </si>
-  <si>
     <t>我們這裡原本是一家修理工坊，社區中家家戶戶的"核芯"若出現任何故障，通常都會交由我們處理。</t>
   </si>
   <si>
@@ -146,12 +126,6 @@
   </si>
   <si>
     <t>但因為襲擊帶來的影響還未結......</t>
-  </si>
-  <si>
-    <t>刺耳的廣播聲驟然響起，生生割裂了兩人的對話。</t>
-  </si>
-  <si>
-    <t>露易絲</t>
   </si>
   <si>
     <t>客人來了，等完成今天的工作後有的是時間解釋。</t>
@@ -341,77 +315,18 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>……</t>
-  </si>
-  <si>
-    <t>這裡是研究員#＆#＆@，呼叫A13外派地球研究小組，收到請回答。</t>
-  </si>
-  <si>
-    <t>約342個小時前，由於一場未知菌種感染的生物襲擊，我與隊伍失聯，現於廢棄建築內等待救援。</t>
-  </si>
-  <si>
-    <t>另外，在該地區發現與人類特質相似，擁有智慧、語言溝通能力的生物，初步交流暫未對我產生攻擊行為或威脅，態度友善。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>以上。呼叫A13外派地球研究小組，收到請回答。</t>
-  </si>
-  <si>
-    <t>寂靜的回電過於嘮叨，她忍無可忍地停下通訊，修復後的通訊儀器猶如溺水者咳出肺泡中的鹹腥一般，不斷吐出低沉或是高亢的雜訊與音節。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>唯獨沒有：A13收到回覆，將立即派往支援......</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">我沒事，通訊設備也沒事，我只是想確認下機器運行之後沒有出現其他問題。 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>她在撒謊，但現在還無人知道。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>黏膩的滑行聲又靠近了些，伴隨著一聲放心的嘆息。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">原來如此，辛苦您了，博士。 </t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>蛇？或是水管？</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>其實說是海洋軟體生物的腕足更貼切，青澀稚嫩的少女聲線出自一個非人形的智慧生命體。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>光滑的表皮上不只有黏液的透亮，兩顆荒誕到有點詭異的豆豆眼，被點在那個生物當作臉部的部位之上。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>詭異的令人發笑，細看甚至還有點可愛？</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>是跟你們之前說要給我的工作有關？</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>近距離觀察後，她保證不論兩顆小黑點的來源是什麼都不重要——它們的本質與初見的印象一般直白的荒唐，只是畫上去的，就像小孩子給氣球狗點睛。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>不似她在地球百科上見過的任何一種生物，反而更偏向某種劣質兒童玩具的存在又晃了晃身軀朝她更接近了些。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉</t>
-  </si>
-  <si>
     <t>？？？？？？</t>
   </si>
   <si>
@@ -446,62 +361,170 @@
     <t>插分圖2</t>
   </si>
   <si>
-    <t>露易絲普(暗).png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉普.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>露易絲普(暗).png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉普.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>露易絲普.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉普(暗).png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>露易絲普(暗).png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉普(暗).png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉普.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉普.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉普(暗).png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>露易絲普(暗).png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>露易絲Louise</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉Klarra</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉喜悅.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉疑問.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>露易絲dk.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>露易絲.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>露易絲疑惑.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉dk.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉喜悅dk.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>露易絲疑惑dk.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉悲傷.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉悲傷dk.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#FFFFFF&gt;……&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#FFFFFF&gt;這裡是研究員#＆#＆@，呼叫A13外派地球研究小組，收到請回答。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#FFFFFF&gt;約342個小時前，由於一場未知菌種感染的生物襲擊，我與隊伍失聯，現於廢棄建築內等待救援。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#FFFFFF&gt;另外，在該地區發現與人類特質相似，擁有智慧、語言溝通能力的生物，初步交流暫未對我產生攻擊行為或威脅，態度友善。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#FFFFFF&gt;以上。呼叫A13外派地球研究小組，收到請回答。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bg暫時1.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑幕裂痕.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑幕通訊.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;寂靜的回電過於嘮叨，她忍無可忍地停下通訊，修復後的通訊儀器猶如溺水者咳出肺泡中的鹹腥一般，不斷吐出低沉或是高亢的雜訊與音節。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;唯獨沒有：A13收到回覆，將立即派往支援......&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;來自17、18歲年輕女性，靦腆中又帶著敬重的語調，並非透過訊號傳遞，而是透過空氣中的震動，切實的扣嚮耳膜。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;她在撒謊，但現在還無人知道。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;黏膩的滑行聲又靠近了些，伴隨著一聲放心的嘆息。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;蛇？或是水管？&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;其實說是海洋軟體生物的腕足更貼切，青澀稚嫩的少女聲線出自一個非人形的智慧生命體。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;光滑的表皮上不只有黏液的透亮，兩顆荒誕到有點詭異的豆豆眼，被點在那個生物當作臉部的部位之上。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;詭異的令人發笑，細看甚至還有點可愛？&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;露易絲的嘴角抽搐了一剎，很快又歸於平靜。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;近距離觀察後，她保證不論兩顆小黑點的來源是什麼都不重要——它們的本質與初見的印象一般直白的荒唐，只是畫上去的，就像小孩子給氣球狗點睛。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;垂掛在充當脖頸處的曲折，是露易絲在企業最熟悉不過的物件──工牌。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;不似她在地球百科上見過的任何一種生物，反而更偏向某種劣質兒童玩具的存在又晃了晃身軀朝她更接近了些。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;助理：克拉拉。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;(......社區，在我來到這裡之後他們不只一次提過，雖然現在看不出來，但這裡以前是小有規模的聚落嗎？)&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;克拉拉頷首表示推理正確。露易絲不確定在襲擊事件發生後，她究竟走了多遠才抵達現在的落腳處，但14個日落的路程評估也是不少的距離。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;——襲擊事件的範圍比預想的大上不少，並不是特別針對他們外來者的攻擊，而是自然災害？&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;刺耳的廣播聲驟然響起，生生割裂了兩人的對話。&lt;/color&gt;</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1096,7 +1119,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1123,12 +1146,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1177,6 +1194,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF551B1B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1484,18 +1506,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1506,19 +1528,19 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1529,19 +1551,19 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1552,16 +1574,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1572,15 +1594,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="122.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="122.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1597,13 +1619,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1611,22 +1633,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1634,22 +1656,22 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1657,19 +1679,19 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1680,17 +1702,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="35.88671875" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="1" max="1" width="5.125" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="35.875" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1707,13 +1729,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="48.6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1721,7 +1743,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1733,10 +1755,10 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1744,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1766,14 +1788,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="81.109375" customWidth="1"/>
+    <col min="3" max="3" width="81.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1790,13 +1812,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1804,7 +1826,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1826,14 +1848,14 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="183.77734375" customWidth="1"/>
+    <col min="3" max="3" width="183.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1850,13 +1872,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1864,7 +1886,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1879,7 +1901,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1887,7 +1909,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1909,15 +1931,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1934,21 +1956,21 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -1960,10 +1982,10 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1971,7 +1993,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1993,21 +2015,22 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N62"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
-    <col min="3" max="3" width="90.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="29.5" customWidth="1"/>
+    <col min="3" max="3" width="90.375" customWidth="1"/>
+    <col min="4" max="4" width="16.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="12" max="12" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2016,46 +2039,46 @@
         <v>0</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="F1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="J1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K1" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="L1" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="M1" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -2064,25 +2087,25 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K2" t="s">
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -2091,25 +2114,25 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
       </c>
       <c r="L3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="97.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -2118,7 +2141,7 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
         <v>5</v>
@@ -2127,16 +2150,16 @@
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -2145,25 +2168,25 @@
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K5" t="s">
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="6" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -2172,19 +2195,19 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K6" t="s">
         <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2199,22 +2222,22 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K7" t="s">
         <v>12</v>
       </c>
       <c r="L7" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2229,25 +2252,25 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J8" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s">
         <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="7" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -2256,25 +2279,25 @@
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
         <v>12</v>
       </c>
       <c r="L9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -2283,19 +2306,19 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s">
         <v>12</v>
       </c>
       <c r="L10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2306,25 +2329,25 @@
         <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J11" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K11" t="s">
         <v>12</v>
       </c>
       <c r="L11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2335,52 +2358,52 @@
         <v>14</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J12" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s">
         <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="7" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="F13" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J13" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s">
         <v>12</v>
       </c>
       <c r="L13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2388,102 +2411,102 @@
         <v>15</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K14" t="s">
         <v>12</v>
       </c>
       <c r="L14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J15" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K15" t="s">
         <v>12</v>
       </c>
       <c r="L15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J16" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K16" t="s">
         <v>12</v>
       </c>
       <c r="L16" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J17" t="s">
         <v>5</v>
@@ -2492,10 +2515,10 @@
         <v>12</v>
       </c>
       <c r="L17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2503,16 +2526,16 @@
         <v>15</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
+        <v>82</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J18" t="s">
         <v>5</v>
@@ -2521,28 +2544,28 @@
         <v>12</v>
       </c>
       <c r="L18" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>12</v>
+        <v>120</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J19" t="s">
         <v>5</v>
@@ -2551,52 +2574,52 @@
         <v>12</v>
       </c>
       <c r="L19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
+        <v>121</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J20" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="K20" t="s">
         <v>12</v>
       </c>
       <c r="L20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" t="s">
-        <v>12</v>
+        <v>122</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J21" t="s">
         <v>5</v>
@@ -2605,52 +2628,52 @@
         <v>12</v>
       </c>
       <c r="L21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" t="s">
-        <v>12</v>
+        <v>123</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J22" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K22" t="s">
         <v>12</v>
       </c>
       <c r="L22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="7" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="F23" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J23" t="s">
         <v>5</v>
@@ -2659,56 +2682,56 @@
         <v>12</v>
       </c>
       <c r="L23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J24" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K24" t="s">
         <v>12</v>
       </c>
       <c r="L24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J25" t="s">
         <v>5</v>
@@ -2717,25 +2740,25 @@
         <v>12</v>
       </c>
       <c r="L25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J26" t="s">
         <v>5</v>
@@ -2744,108 +2767,108 @@
         <v>12</v>
       </c>
       <c r="L26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J27" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="K27" t="s">
         <v>12</v>
       </c>
       <c r="L27" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K28" t="s">
         <v>12</v>
       </c>
       <c r="L28" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J29" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s">
         <v>12</v>
       </c>
       <c r="L29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>126</v>
+        <v>18</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J30" t="s">
         <v>5</v>
@@ -2854,27 +2877,27 @@
         <v>12</v>
       </c>
       <c r="L30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J31" t="s">
         <v>5</v>
@@ -2883,114 +2906,114 @@
         <v>12</v>
       </c>
       <c r="L31" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J32" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="K32" t="s">
         <v>12</v>
       </c>
       <c r="L32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J33" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K33" t="s">
         <v>12</v>
       </c>
       <c r="L33" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F34" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J34" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K34" t="s">
         <v>12</v>
       </c>
       <c r="L34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J35" t="s">
         <v>5</v>
@@ -2999,27 +3022,27 @@
         <v>12</v>
       </c>
       <c r="L35" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J36" t="s">
         <v>5</v>
@@ -3028,81 +3051,81 @@
         <v>12</v>
       </c>
       <c r="L36" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J37" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K37" t="s">
         <v>12</v>
       </c>
       <c r="L37" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="6" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J38" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K38" t="s">
         <v>12</v>
       </c>
       <c r="L38" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="6" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J39" t="s">
         <v>5</v>
@@ -3111,27 +3134,27 @@
         <v>12</v>
       </c>
       <c r="L39" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J40" t="s">
         <v>5</v>
@@ -3140,117 +3163,117 @@
         <v>12</v>
       </c>
       <c r="L40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J41" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K41" t="s">
         <v>12</v>
       </c>
       <c r="L41" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="N41" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="F42" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J42" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K42" t="s">
         <v>12</v>
       </c>
       <c r="L42" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="F43" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J43" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K43" t="s">
         <v>12</v>
       </c>
       <c r="L43" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="F44" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J44" t="s">
         <v>5</v>
@@ -3259,45 +3282,45 @@
         <v>12</v>
       </c>
       <c r="L44" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="7" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J45" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K45" t="s">
         <v>12</v>
       </c>
       <c r="L45" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
@@ -3306,7 +3329,7 @@
         <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J46" t="s">
         <v>5</v>
@@ -3315,21 +3338,21 @@
         <v>12</v>
       </c>
       <c r="L46" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="N46" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
@@ -3338,27 +3361,27 @@
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J47" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K47" t="s">
         <v>12</v>
       </c>
       <c r="L47" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
@@ -3367,27 +3390,27 @@
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J48" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K48" t="s">
         <v>12</v>
       </c>
       <c r="L48" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="9" t="s">
-        <v>42</v>
+      <c r="B49" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -3396,27 +3419,27 @@
         <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J49" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K49" t="s">
         <v>12</v>
       </c>
       <c r="L49" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="9" t="s">
-        <v>42</v>
+      <c r="B50" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
@@ -3425,27 +3448,27 @@
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J50" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K50" t="s">
         <v>12</v>
       </c>
       <c r="L50" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>45</v>
+      <c r="B51" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
@@ -3454,27 +3477,27 @@
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J51" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K51" t="s">
         <v>12</v>
       </c>
       <c r="L51" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" s="9" t="s">
-        <v>47</v>
+      <c r="B52" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D52" t="s">
         <v>12</v>
@@ -3483,27 +3506,27 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J52" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="K52" t="s">
         <v>12</v>
       </c>
       <c r="L52" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" s="9" t="s">
-        <v>47</v>
+      <c r="B53" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D53" t="s">
         <v>12</v>
@@ -3512,30 +3535,30 @@
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J53" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K53" t="s">
         <v>12</v>
       </c>
       <c r="L53" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="N53" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" s="9" t="s">
-        <v>45</v>
+      <c r="B54" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
         <v>12</v>
@@ -3544,7 +3567,7 @@
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J54" t="s">
         <v>5</v>
@@ -3553,18 +3576,18 @@
         <v>12</v>
       </c>
       <c r="L54" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>47</v>
+      <c r="B55" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D55" t="s">
         <v>12</v>
@@ -3573,7 +3596,7 @@
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J55" t="s">
         <v>5</v>
@@ -3582,18 +3605,18 @@
         <v>12</v>
       </c>
       <c r="L55" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" s="9" t="s">
-        <v>42</v>
+      <c r="B56" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
@@ -3602,7 +3625,7 @@
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J56" t="s">
         <v>5</v>
@@ -3611,18 +3634,18 @@
         <v>12</v>
       </c>
       <c r="L56" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>45</v>
+      <c r="B57" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D57" t="s">
         <v>12</v>
@@ -3631,7 +3654,7 @@
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J57" t="s">
         <v>5</v>
@@ -3640,18 +3663,18 @@
         <v>12</v>
       </c>
       <c r="L57" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="9" t="s">
-        <v>42</v>
+      <c r="B58" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D58" t="s">
         <v>12</v>
@@ -3660,7 +3683,7 @@
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J58" t="s">
         <v>5</v>
@@ -3669,18 +3692,18 @@
         <v>12</v>
       </c>
       <c r="L58" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" s="9" t="s">
-        <v>42</v>
+      <c r="B59" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D59" t="s">
         <v>12</v>
@@ -3689,7 +3712,7 @@
         <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J59" t="s">
         <v>5</v>
@@ -3698,18 +3721,18 @@
         <v>12</v>
       </c>
       <c r="L59" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>42</v>
+      <c r="B60" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D60" t="s">
         <v>12</v>
@@ -3718,7 +3741,7 @@
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J60" t="s">
         <v>5</v>
@@ -3727,18 +3750,18 @@
         <v>12</v>
       </c>
       <c r="L60" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" s="9" t="s">
-        <v>42</v>
+      <c r="B61" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D61" t="s">
         <v>12</v>
@@ -3747,7 +3770,7 @@
         <v>12</v>
       </c>
       <c r="F61" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J61" t="s">
         <v>5</v>
@@ -3756,18 +3779,18 @@
         <v>12</v>
       </c>
       <c r="L61" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" s="9" t="s">
-        <v>42</v>
+      <c r="B62" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D62" t="s">
         <v>12</v>
@@ -3776,7 +3799,7 @@
         <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J62" t="s">
         <v>5</v>
@@ -3785,7 +3808,7 @@
         <v>12</v>
       </c>
       <c r="L62" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B153607-8F59-41EB-89B9-FDF7F48F8906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C6A746-B877-45E6-A7DD-AA8DE81FAEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="860" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="134">
   <si>
     <t>對話內容</t>
   </si>
@@ -377,10 +377,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>克拉拉疑問.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>露易絲dk.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -518,6 +514,14 @@
   </si>
   <si>
     <t>&lt;color=#61494E&gt;刺耳的廣播聲驟然響起，生生割裂了兩人的對話。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉疑惑.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉疑惑dk.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2078,7 +2082,7 @@
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -2096,7 +2100,7 @@
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -2105,7 +2109,7 @@
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -2123,7 +2127,7 @@
         <v>12</v>
       </c>
       <c r="L3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="97.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -2132,7 +2136,7 @@
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -2150,7 +2154,7 @@
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2159,7 +2163,7 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -2177,7 +2181,7 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -2186,7 +2190,7 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -2204,7 +2208,7 @@
         <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2231,7 +2235,7 @@
         <v>12</v>
       </c>
       <c r="L7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>71</v>
@@ -2261,7 +2265,7 @@
         <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2270,7 +2274,7 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -2288,7 +2292,7 @@
         <v>12</v>
       </c>
       <c r="L9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2297,7 +2301,7 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -2315,7 +2319,7 @@
         <v>12</v>
       </c>
       <c r="L10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2329,7 +2333,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>96</v>
@@ -2344,7 +2348,7 @@
         <v>12</v>
       </c>
       <c r="L11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2358,10 +2362,10 @@
         <v>14</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s">
         <v>72</v>
@@ -2373,7 +2377,7 @@
         <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2382,13 +2386,13 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F13" t="s">
         <v>72</v>
@@ -2400,7 +2404,7 @@
         <v>12</v>
       </c>
       <c r="L13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2414,10 +2418,10 @@
         <v>16</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="F14" t="s">
         <v>72</v>
@@ -2429,7 +2433,7 @@
         <v>12</v>
       </c>
       <c r="L14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -2443,10 +2447,10 @@
         <v>81</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="F15" t="s">
         <v>51</v>
@@ -2458,7 +2462,7 @@
         <v>12</v>
       </c>
       <c r="L15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2467,13 +2471,13 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="F16" t="s">
         <v>51</v>
@@ -2485,7 +2489,7 @@
         <v>12</v>
       </c>
       <c r="L16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>74</v>
@@ -2497,13 +2501,13 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F17" t="s">
         <v>51</v>
@@ -2515,7 +2519,7 @@
         <v>12</v>
       </c>
       <c r="L17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2529,7 +2533,7 @@
         <v>82</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>96</v>
@@ -2544,7 +2548,7 @@
         <v>12</v>
       </c>
       <c r="L18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>70</v>
@@ -2556,10 +2560,10 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>96</v>
@@ -2574,7 +2578,7 @@
         <v>12</v>
       </c>
       <c r="L19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2583,10 +2587,10 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>96</v>
@@ -2601,7 +2605,7 @@
         <v>12</v>
       </c>
       <c r="L20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2610,10 +2614,10 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>96</v>
@@ -2628,7 +2632,7 @@
         <v>12</v>
       </c>
       <c r="L21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -2637,10 +2641,10 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>96</v>
@@ -2655,7 +2659,7 @@
         <v>12</v>
       </c>
       <c r="L22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -2664,13 +2668,13 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F23" t="s">
         <v>51</v>
@@ -2682,7 +2686,7 @@
         <v>12</v>
       </c>
       <c r="L23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -2696,10 +2700,10 @@
         <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="F24" t="s">
         <v>51</v>
@@ -2711,7 +2715,7 @@
         <v>12</v>
       </c>
       <c r="L24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -2725,10 +2729,10 @@
         <v>83</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="F25" t="s">
         <v>51</v>
@@ -2740,7 +2744,7 @@
         <v>12</v>
       </c>
       <c r="L25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2749,7 +2753,7 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
@@ -2767,7 +2771,7 @@
         <v>12</v>
       </c>
       <c r="L26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2776,7 +2780,7 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
@@ -2794,7 +2798,7 @@
         <v>12</v>
       </c>
       <c r="L27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2803,7 +2807,7 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
@@ -2821,7 +2825,7 @@
         <v>12</v>
       </c>
       <c r="L28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2830,7 +2834,7 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
@@ -2848,7 +2852,7 @@
         <v>12</v>
       </c>
       <c r="L29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2877,7 +2881,7 @@
         <v>12</v>
       </c>
       <c r="L30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2891,7 +2895,7 @@
         <v>19</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>96</v>
@@ -2906,7 +2910,7 @@
         <v>12</v>
       </c>
       <c r="L31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -2917,13 +2921,13 @@
         <v>94</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F32" t="s">
         <v>51</v>
@@ -2935,7 +2939,7 @@
         <v>12</v>
       </c>
       <c r="L32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -2949,10 +2953,10 @@
         <v>20</v>
       </c>
       <c r="D33" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="F33" t="s">
         <v>51</v>
@@ -2964,7 +2968,7 @@
         <v>12</v>
       </c>
       <c r="L33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -2978,10 +2982,10 @@
         <v>21</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F34" t="s">
         <v>51</v>
@@ -2993,7 +2997,7 @@
         <v>12</v>
       </c>
       <c r="L34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -3007,10 +3011,10 @@
         <v>22</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F35" t="s">
         <v>51</v>
@@ -3022,7 +3026,7 @@
         <v>12</v>
       </c>
       <c r="L35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -3036,10 +3040,10 @@
         <v>23</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F36" t="s">
         <v>51</v>
@@ -3051,7 +3055,7 @@
         <v>12</v>
       </c>
       <c r="L36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -3065,10 +3069,10 @@
         <v>24</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F37" t="s">
         <v>51</v>
@@ -3080,7 +3084,7 @@
         <v>12</v>
       </c>
       <c r="L37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -3089,13 +3093,13 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" t="s">
         <v>51</v>
@@ -3107,7 +3111,7 @@
         <v>12</v>
       </c>
       <c r="L38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="33" x14ac:dyDescent="0.25">
@@ -3116,13 +3120,13 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>51</v>
@@ -3134,7 +3138,7 @@
         <v>12</v>
       </c>
       <c r="L39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -3148,10 +3152,10 @@
         <v>25</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F40" t="s">
         <v>51</v>
@@ -3163,7 +3167,7 @@
         <v>12</v>
       </c>
       <c r="L40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -3177,10 +3181,10 @@
         <v>26</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F41" t="s">
         <v>51</v>
@@ -3192,7 +3196,7 @@
         <v>12</v>
       </c>
       <c r="L41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N41" t="s">
         <v>79</v>
@@ -3209,10 +3213,10 @@
         <v>27</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F42" t="s">
         <v>51</v>
@@ -3224,7 +3228,7 @@
         <v>12</v>
       </c>
       <c r="L42" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -3238,10 +3242,10 @@
         <v>28</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F43" t="s">
         <v>51</v>
@@ -3253,7 +3257,7 @@
         <v>12</v>
       </c>
       <c r="L43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -3267,10 +3271,10 @@
         <v>29</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F44" t="s">
         <v>51</v>
@@ -3282,7 +3286,7 @@
         <v>12</v>
       </c>
       <c r="L44" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -3291,13 +3295,13 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
         <v>51</v>
@@ -3309,7 +3313,7 @@
         <v>12</v>
       </c>
       <c r="L45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -3338,7 +3342,7 @@
         <v>12</v>
       </c>
       <c r="L46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N46" t="s">
         <v>80</v>
@@ -3370,7 +3374,7 @@
         <v>12</v>
       </c>
       <c r="L47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -3399,7 +3403,7 @@
         <v>12</v>
       </c>
       <c r="L48" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -3428,7 +3432,7 @@
         <v>12</v>
       </c>
       <c r="L49" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -3457,7 +3461,7 @@
         <v>12</v>
       </c>
       <c r="L50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -3486,7 +3490,7 @@
         <v>12</v>
       </c>
       <c r="L51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -3515,7 +3519,7 @@
         <v>12</v>
       </c>
       <c r="L52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -3544,7 +3548,7 @@
         <v>12</v>
       </c>
       <c r="L53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N53" t="s">
         <v>53</v>
@@ -3576,7 +3580,7 @@
         <v>12</v>
       </c>
       <c r="L54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -3605,7 +3609,7 @@
         <v>12</v>
       </c>
       <c r="L55" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -3634,7 +3638,7 @@
         <v>12</v>
       </c>
       <c r="L56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -3663,7 +3667,7 @@
         <v>12</v>
       </c>
       <c r="L57" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -3692,7 +3696,7 @@
         <v>12</v>
       </c>
       <c r="L58" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -3721,7 +3725,7 @@
         <v>12</v>
       </c>
       <c r="L59" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -3750,7 +3754,7 @@
         <v>12</v>
       </c>
       <c r="L60" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -3779,7 +3783,7 @@
         <v>12</v>
       </c>
       <c r="L61" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -3808,7 +3812,7 @@
         <v>12</v>
       </c>
       <c r="L62" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C6A746-B877-45E6-A7DD-AA8DE81FAEFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71115F7-2528-4FFA-A408-DB50B4E564B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="860" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="140">
   <si>
     <t>對話內容</t>
   </si>
@@ -522,6 +522,30 @@
   </si>
   <si>
     <t>克拉拉疑惑dk.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景音樂</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>特效音</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>musicuse</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>slide</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>tap</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -698,7 +722,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -878,6 +902,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1123,7 +1153,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1150,6 +1180,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1512,16 +1545,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1544,7 +1577,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1567,7 +1600,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1600,13 +1633,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="122.125" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="122.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1629,7 +1662,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1652,7 +1685,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1675,7 +1708,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1708,15 +1741,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="35.875" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="35.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1739,7 +1772,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1762,7 +1795,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1794,12 +1827,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="81.125" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1822,7 +1855,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1854,12 +1887,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="183.75" customWidth="1"/>
+    <col min="3" max="3" width="183.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1882,7 +1915,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1905,7 +1938,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1937,13 +1970,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1966,7 +1999,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1989,7 +2022,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2020,19 +2053,21 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:N62"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P62"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.5" customWidth="1"/>
-    <col min="3" max="3" width="90.375" customWidth="1"/>
-    <col min="4" max="4" width="16.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="90.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="12" max="12" width="14.25" customWidth="1"/>
+    <col min="12" max="12" width="14.21875" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>67</v>
       </c>
@@ -2075,8 +2110,14 @@
       <c r="N1" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2102,8 +2143,11 @@
       <c r="L2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2129,8 +2173,14 @@
       <c r="L3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="97.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O3" t="s">
+        <v>139</v>
+      </c>
+      <c r="P3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2156,8 +2206,14 @@
       <c r="L4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+      <c r="O4" t="s">
+        <v>136</v>
+      </c>
+      <c r="P4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2184,7 +2240,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2211,7 +2267,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2241,7 +2297,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2268,7 +2324,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2295,7 +2351,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2322,7 +2378,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2351,7 +2407,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2380,7 +2436,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2407,7 +2463,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2436,7 +2492,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2465,7 +2521,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2495,7 +2551,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2522,7 +2578,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2554,7 +2610,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2581,7 +2637,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2608,7 +2664,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2635,7 +2691,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2662,7 +2718,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2689,7 +2745,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2718,7 +2774,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2747,7 +2803,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2774,7 +2830,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2801,7 +2857,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2828,7 +2884,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2855,7 +2911,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2884,7 +2940,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2913,7 +2969,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2942,7 +2998,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2971,7 +3027,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3000,7 +3056,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3029,7 +3085,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3058,7 +3114,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3087,7 +3143,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3114,7 +3170,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3141,7 +3197,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3170,7 +3226,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3202,7 +3258,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3231,7 +3287,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3260,7 +3316,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3289,7 +3345,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3316,7 +3372,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3348,7 +3404,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3377,7 +3433,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3406,7 +3462,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3435,7 +3491,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3464,7 +3520,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3493,7 +3549,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3522,7 +3578,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3554,7 +3610,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3583,7 +3639,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3612,7 +3668,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3641,7 +3697,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3670,7 +3726,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3699,7 +3755,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3728,7 +3784,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3757,7 +3813,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3786,7 +3842,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>

--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71115F7-2528-4FFA-A408-DB50B4E564B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="860" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="860" firstSheet="6" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -433,10 +432,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Bg暫時1.jpg</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>黑幕裂痕.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -546,13 +541,17 @@
   </si>
   <si>
     <t>BGM1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>比較亮.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1543,7 +1542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1631,7 +1630,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1739,7 +1738,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1825,7 +1824,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1885,7 +1884,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1968,7 +1967,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2052,7 +2051,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P62"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2111,10 +2110,10 @@
         <v>71</v>
       </c>
       <c r="O1" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" s="9" t="s">
         <v>134</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -2141,10 +2140,10 @@
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -2171,13 +2170,13 @@
         <v>12</v>
       </c>
       <c r="L3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2204,13 +2203,13 @@
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
@@ -2237,7 +2236,7 @@
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
@@ -2264,7 +2263,7 @@
         <v>12</v>
       </c>
       <c r="L6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
@@ -2291,7 +2290,7 @@
         <v>12</v>
       </c>
       <c r="L7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>71</v>
@@ -2321,7 +2320,7 @@
         <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
@@ -2330,7 +2329,7 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -2348,7 +2347,7 @@
         <v>12</v>
       </c>
       <c r="L9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
@@ -2357,7 +2356,7 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -2375,7 +2374,7 @@
         <v>12</v>
       </c>
       <c r="L10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
@@ -2404,7 +2403,7 @@
         <v>12</v>
       </c>
       <c r="L11" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -2433,7 +2432,7 @@
         <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
@@ -2442,7 +2441,7 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>97</v>
@@ -2460,7 +2459,7 @@
         <v>12</v>
       </c>
       <c r="L13" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
@@ -2477,7 +2476,7 @@
         <v>97</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F14" t="s">
         <v>72</v>
@@ -2489,7 +2488,7 @@
         <v>12</v>
       </c>
       <c r="L14" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -2506,7 +2505,7 @@
         <v>98</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F15" t="s">
         <v>51</v>
@@ -2518,7 +2517,7 @@
         <v>12</v>
       </c>
       <c r="L15" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
@@ -2527,13 +2526,13 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>97</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F16" t="s">
         <v>51</v>
@@ -2545,7 +2544,7 @@
         <v>12</v>
       </c>
       <c r="L16" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>74</v>
@@ -2557,7 +2556,7 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>98</v>
@@ -2575,7 +2574,7 @@
         <v>12</v>
       </c>
       <c r="L17" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2604,7 +2603,7 @@
         <v>12</v>
       </c>
       <c r="L18" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>70</v>
@@ -2616,7 +2615,7 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>97</v>
@@ -2634,7 +2633,7 @@
         <v>12</v>
       </c>
       <c r="L19" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2643,7 +2642,7 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>97</v>
@@ -2661,7 +2660,7 @@
         <v>12</v>
       </c>
       <c r="L20" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2670,7 +2669,7 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>97</v>
@@ -2688,7 +2687,7 @@
         <v>12</v>
       </c>
       <c r="L21" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -2697,7 +2696,7 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>97</v>
@@ -2715,7 +2714,7 @@
         <v>12</v>
       </c>
       <c r="L22" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -2724,7 +2723,7 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>97</v>
@@ -2742,7 +2741,7 @@
         <v>12</v>
       </c>
       <c r="L23" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -2771,7 +2770,7 @@
         <v>12</v>
       </c>
       <c r="L24" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2800,7 +2799,7 @@
         <v>12</v>
       </c>
       <c r="L25" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2809,7 +2808,7 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
@@ -2827,7 +2826,7 @@
         <v>12</v>
       </c>
       <c r="L26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2836,7 +2835,7 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
@@ -2854,7 +2853,7 @@
         <v>12</v>
       </c>
       <c r="L27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2863,7 +2862,7 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
@@ -2881,7 +2880,7 @@
         <v>12</v>
       </c>
       <c r="L28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2890,7 +2889,7 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
@@ -2908,7 +2907,7 @@
         <v>12</v>
       </c>
       <c r="L29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2937,7 +2936,7 @@
         <v>12</v>
       </c>
       <c r="L30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2966,7 +2965,7 @@
         <v>12</v>
       </c>
       <c r="L31" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2977,7 +2976,7 @@
         <v>94</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>99</v>
@@ -2995,7 +2994,7 @@
         <v>12</v>
       </c>
       <c r="L32" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -3024,7 +3023,7 @@
         <v>12</v>
       </c>
       <c r="L33" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -3053,7 +3052,7 @@
         <v>12</v>
       </c>
       <c r="L34" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -3082,7 +3081,7 @@
         <v>12</v>
       </c>
       <c r="L35" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -3111,7 +3110,7 @@
         <v>12</v>
       </c>
       <c r="L36" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -3140,7 +3139,7 @@
         <v>12</v>
       </c>
       <c r="L37" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -3149,7 +3148,7 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>97</v>
@@ -3167,7 +3166,7 @@
         <v>12</v>
       </c>
       <c r="L38" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -3176,7 +3175,7 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>97</v>
@@ -3194,7 +3193,7 @@
         <v>12</v>
       </c>
       <c r="L39" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -3223,7 +3222,7 @@
         <v>12</v>
       </c>
       <c r="L40" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -3252,7 +3251,7 @@
         <v>12</v>
       </c>
       <c r="L41" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="N41" t="s">
         <v>79</v>
@@ -3284,7 +3283,7 @@
         <v>12</v>
       </c>
       <c r="L42" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -3313,7 +3312,7 @@
         <v>12</v>
       </c>
       <c r="L43" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -3342,7 +3341,7 @@
         <v>12</v>
       </c>
       <c r="L44" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -3351,7 +3350,7 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>97</v>
@@ -3369,7 +3368,7 @@
         <v>12</v>
       </c>
       <c r="L45" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -3398,7 +3397,7 @@
         <v>12</v>
       </c>
       <c r="L46" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N46" t="s">
         <v>80</v>
@@ -3430,7 +3429,7 @@
         <v>12</v>
       </c>
       <c r="L47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -3459,7 +3458,7 @@
         <v>12</v>
       </c>
       <c r="L48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -3488,7 +3487,7 @@
         <v>12</v>
       </c>
       <c r="L49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -3517,7 +3516,7 @@
         <v>12</v>
       </c>
       <c r="L50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -3546,7 +3545,7 @@
         <v>12</v>
       </c>
       <c r="L51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -3575,7 +3574,7 @@
         <v>12</v>
       </c>
       <c r="L52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -3604,7 +3603,7 @@
         <v>12</v>
       </c>
       <c r="L53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N53" t="s">
         <v>53</v>
@@ -3636,7 +3635,7 @@
         <v>12</v>
       </c>
       <c r="L54" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
@@ -3665,7 +3664,7 @@
         <v>12</v>
       </c>
       <c r="L55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
@@ -3694,7 +3693,7 @@
         <v>12</v>
       </c>
       <c r="L56" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
@@ -3723,7 +3722,7 @@
         <v>12</v>
       </c>
       <c r="L57" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
@@ -3752,7 +3751,7 @@
         <v>12</v>
       </c>
       <c r="L58" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
@@ -3781,7 +3780,7 @@
         <v>12</v>
       </c>
       <c r="L59" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
@@ -3810,7 +3809,7 @@
         <v>12</v>
       </c>
       <c r="L60" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
@@ -3839,7 +3838,7 @@
         <v>12</v>
       </c>
       <c r="L61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
@@ -3868,7 +3867,7 @@
         <v>12</v>
       </c>
       <c r="L62" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="142">
   <si>
     <t>對話內容</t>
   </si>
@@ -545,6 +545,14 @@
   </si>
   <si>
     <t>比較亮.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>小怪物監視器01.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>小怪物監視器01.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -3603,7 +3611,7 @@
         <v>12</v>
       </c>
       <c r="L53" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="N53" t="s">
         <v>53</v>
@@ -3635,7 +3643,7 @@
         <v>12</v>
       </c>
       <c r="L54" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
@@ -3664,7 +3672,7 @@
         <v>12</v>
       </c>
       <c r="L55" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
@@ -3693,7 +3701,7 @@
         <v>12</v>
       </c>
       <c r="L56" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
@@ -3722,7 +3730,7 @@
         <v>12</v>
       </c>
       <c r="L57" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
@@ -3751,7 +3759,7 @@
         <v>12</v>
       </c>
       <c r="L58" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
@@ -3780,7 +3788,7 @@
         <v>12</v>
       </c>
       <c r="L59" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
@@ -3809,7 +3817,7 @@
         <v>12</v>
       </c>
       <c r="L60" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
@@ -3838,7 +3846,7 @@
         <v>12</v>
       </c>
       <c r="L61" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
@@ -3867,7 +3875,7 @@
         <v>12</v>
       </c>
       <c r="L62" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="145">
   <si>
     <t>對話內容</t>
   </si>
@@ -528,22 +528,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>musicuse</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>slide</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>tap</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>比較亮.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -552,8 +536,31 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>小怪物監視器01.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>無線電雜音</t>
+  </si>
+  <si>
+    <t>黏液爬行聲</t>
+  </si>
+  <si>
+    <t>廣播提示音</t>
+  </si>
+  <si>
+    <t>電視旋鈕</t>
+  </si>
+  <si>
+    <t>Quiet_Days</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mercury_Fiction</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>無線電雜音2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>拍打</t>
   </si>
 </sst>
 </file>
@@ -2150,9 +2157,6 @@
       <c r="L2" t="s">
         <v>111</v>
       </c>
-      <c r="O2" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -2180,11 +2184,8 @@
       <c r="L3" t="s">
         <v>111</v>
       </c>
-      <c r="O3" t="s">
-        <v>138</v>
-      </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2213,12 +2214,6 @@
       <c r="L4" t="s">
         <v>111</v>
       </c>
-      <c r="O4" t="s">
-        <v>135</v>
-      </c>
-      <c r="P4" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="5" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -2273,6 +2268,9 @@
       <c r="L6" t="s">
         <v>111</v>
       </c>
+      <c r="P6" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -2357,6 +2355,9 @@
       <c r="L9" t="s">
         <v>111</v>
       </c>
+      <c r="P9" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -2411,7 +2412,13 @@
         <v>12</v>
       </c>
       <c r="L11" t="s">
-        <v>139</v>
+        <v>135</v>
+      </c>
+      <c r="O11" t="s">
+        <v>141</v>
+      </c>
+      <c r="P11" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
@@ -2440,7 +2447,7 @@
         <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
@@ -2467,7 +2474,7 @@
         <v>12</v>
       </c>
       <c r="L13" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
@@ -2496,7 +2503,7 @@
         <v>12</v>
       </c>
       <c r="L14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -2525,7 +2532,7 @@
         <v>12</v>
       </c>
       <c r="L15" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
@@ -2552,7 +2559,7 @@
         <v>12</v>
       </c>
       <c r="L16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>74</v>
@@ -2582,7 +2589,7 @@
         <v>12</v>
       </c>
       <c r="L17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2611,7 +2618,7 @@
         <v>12</v>
       </c>
       <c r="L18" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>70</v>
@@ -2641,7 +2648,7 @@
         <v>12</v>
       </c>
       <c r="L19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2668,7 +2675,7 @@
         <v>12</v>
       </c>
       <c r="L20" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2695,7 +2702,7 @@
         <v>12</v>
       </c>
       <c r="L21" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -2722,7 +2729,7 @@
         <v>12</v>
       </c>
       <c r="L22" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -2749,7 +2756,7 @@
         <v>12</v>
       </c>
       <c r="L23" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -2778,7 +2785,7 @@
         <v>12</v>
       </c>
       <c r="L24" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2807,7 +2814,7 @@
         <v>12</v>
       </c>
       <c r="L25" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -2973,7 +2980,7 @@
         <v>12</v>
       </c>
       <c r="L31" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
@@ -3002,10 +3009,10 @@
         <v>12</v>
       </c>
       <c r="L32" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3031,10 +3038,10 @@
         <v>12</v>
       </c>
       <c r="L33" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3060,10 +3067,10 @@
         <v>12</v>
       </c>
       <c r="L34" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3089,10 +3096,10 @@
         <v>12</v>
       </c>
       <c r="L35" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3118,10 +3125,10 @@
         <v>12</v>
       </c>
       <c r="L36" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3147,10 +3154,10 @@
         <v>12</v>
       </c>
       <c r="L37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3174,10 +3181,10 @@
         <v>12</v>
       </c>
       <c r="L38" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3201,10 +3208,10 @@
         <v>12</v>
       </c>
       <c r="L39" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3230,10 +3237,10 @@
         <v>12</v>
       </c>
       <c r="L40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3259,13 +3266,13 @@
         <v>12</v>
       </c>
       <c r="L41" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N41" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3291,10 +3298,10 @@
         <v>12</v>
       </c>
       <c r="L42" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3320,10 +3327,10 @@
         <v>12</v>
       </c>
       <c r="L43" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3349,10 +3356,10 @@
         <v>12</v>
       </c>
       <c r="L44" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3376,10 +3383,16 @@
         <v>12</v>
       </c>
       <c r="L45" t="s">
+        <v>135</v>
+      </c>
+      <c r="O45" t="s">
+        <v>142</v>
+      </c>
+      <c r="P45" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3411,7 +3424,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3440,7 +3453,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3469,7 +3482,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3495,10 +3508,13 @@
         <v>12</v>
       </c>
       <c r="L49" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+      <c r="P49" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3524,10 +3540,10 @@
         <v>12</v>
       </c>
       <c r="L50" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3553,10 +3569,10 @@
         <v>12</v>
       </c>
       <c r="L51" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3582,10 +3598,10 @@
         <v>12</v>
       </c>
       <c r="L52" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3611,13 +3627,13 @@
         <v>12</v>
       </c>
       <c r="L53" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N53" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3643,10 +3659,10 @@
         <v>12</v>
       </c>
       <c r="L54" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3672,10 +3688,10 @@
         <v>12</v>
       </c>
       <c r="L55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3701,10 +3717,10 @@
         <v>12</v>
       </c>
       <c r="L56" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3730,10 +3746,10 @@
         <v>12</v>
       </c>
       <c r="L57" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3759,10 +3775,10 @@
         <v>12</v>
       </c>
       <c r="L58" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3788,10 +3804,10 @@
         <v>12</v>
       </c>
       <c r="L59" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3817,10 +3833,10 @@
         <v>12</v>
       </c>
       <c r="L60" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3846,10 +3862,13 @@
         <v>12</v>
       </c>
       <c r="L61" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+      <c r="P61" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3875,7 +3894,10 @@
         <v>12</v>
       </c>
       <c r="L62" t="s">
-        <v>140</v>
+        <v>136</v>
+      </c>
+      <c r="P62" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="148">
   <si>
     <t>對話內容</t>
   </si>
@@ -561,6 +561,18 @@
   </si>
   <si>
     <t>拍打</t>
+  </si>
+  <si>
+    <t>小怪物監視器01.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>小怪物水缸無手.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>小怪物水缸有手.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2076,7 +2088,7 @@
     <col min="5" max="5" width="15.88671875" style="5" customWidth="1"/>
     <col min="6" max="6" width="12.44140625" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="12" max="12" width="14.21875" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" customWidth="1"/>
     <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -3508,7 +3520,7 @@
         <v>12</v>
       </c>
       <c r="L49" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="P49" t="s">
         <v>140</v>
@@ -3688,7 +3700,7 @@
         <v>12</v>
       </c>
       <c r="L55" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
@@ -3717,7 +3729,7 @@
         <v>12</v>
       </c>
       <c r="L56" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
@@ -3746,7 +3758,7 @@
         <v>12</v>
       </c>
       <c r="L57" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
@@ -3775,7 +3787,7 @@
         <v>12</v>
       </c>
       <c r="L58" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
@@ -3804,7 +3816,7 @@
         <v>12</v>
       </c>
       <c r="L59" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
@@ -3833,7 +3845,7 @@
         <v>12</v>
       </c>
       <c r="L60" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
@@ -3862,7 +3874,7 @@
         <v>12</v>
       </c>
       <c r="L61" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P61" t="s">
         <v>144</v>
@@ -3894,7 +3906,7 @@
         <v>12</v>
       </c>
       <c r="L62" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P62" t="s">
         <v>144</v>

--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD84B5AD-A127-4A7C-BC19-0B52A985E86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="860" firstSheet="6" activeTab="6"/>
+    <workbookView xWindow="1785" yWindow="570" windowWidth="19155" windowHeight="15630" tabRatio="860" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="150">
   <si>
     <t>對話內容</t>
   </si>
@@ -572,13 +573,21 @@
   </si>
   <si>
     <t>小怪物水缸有手.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉眼.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉工牌.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1569,18 +1578,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1603,7 +1612,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1626,7 +1635,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1657,15 +1666,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="122.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="122.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1688,7 +1697,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1711,7 +1720,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1734,7 +1743,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1765,17 +1774,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="35.88671875" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="1" max="1" width="5.125" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="35.875" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1798,7 +1807,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1821,7 +1830,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1851,14 +1860,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="81.109375" customWidth="1"/>
+    <col min="3" max="3" width="81.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1881,7 +1890,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1911,14 +1920,14 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="183.77734375" customWidth="1"/>
+    <col min="3" max="3" width="183.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1941,7 +1950,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1964,7 +1973,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1994,15 +2003,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2025,7 +2034,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2048,7 +2057,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2078,22 +2087,22 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:P62"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
-    <col min="3" max="3" width="90.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="29.5" customWidth="1"/>
+    <col min="3" max="3" width="90.375" customWidth="1"/>
+    <col min="4" max="4" width="16.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="12" max="12" width="22.44140625" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.5" customWidth="1"/>
+    <col min="15" max="15" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>67</v>
       </c>
@@ -2143,7 +2152,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2170,7 +2179,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2200,7 +2209,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="97.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2227,7 +2236,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2254,7 +2263,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2284,7 +2293,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2314,7 +2323,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2341,7 +2350,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2371,7 +2380,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2398,7 +2407,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2433,7 +2442,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2462,7 +2471,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2489,7 +2498,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2518,7 +2527,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2547,7 +2556,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2577,7 +2586,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2604,7 +2613,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2636,7 +2645,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2663,7 +2672,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2690,7 +2699,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2717,7 +2726,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2744,7 +2753,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2771,7 +2780,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2800,7 +2809,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2829,7 +2838,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2853,10 +2862,10 @@
         <v>12</v>
       </c>
       <c r="L26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2880,10 +2889,10 @@
         <v>12</v>
       </c>
       <c r="L27" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2907,10 +2916,10 @@
         <v>12</v>
       </c>
       <c r="L28" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2934,10 +2943,10 @@
         <v>12</v>
       </c>
       <c r="L29" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2947,11 +2956,11 @@
       <c r="C30" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
+      <c r="D30" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="F30" t="s">
         <v>51</v>
@@ -2963,10 +2972,10 @@
         <v>12</v>
       </c>
       <c r="L30" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2995,7 +3004,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3024,7 +3033,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3053,7 +3062,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3082,7 +3091,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3111,7 +3120,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3140,7 +3149,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3169,7 +3178,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3196,7 +3205,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3223,7 +3232,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3252,7 +3261,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3284,7 +3293,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3313,7 +3322,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3342,7 +3351,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3371,7 +3380,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3404,7 +3413,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3436,7 +3445,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3465,7 +3474,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3494,7 +3503,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3526,7 +3535,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3555,7 +3564,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3584,7 +3593,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3613,7 +3622,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3645,7 +3654,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3674,7 +3683,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3703,7 +3712,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3732,7 +3741,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3761,7 +3770,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3790,7 +3799,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3819,7 +3828,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3848,7 +3857,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3880,7 +3889,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>

--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD84B5AD-A127-4A7C-BC19-0B52A985E86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="570" windowWidth="19155" windowHeight="15630" tabRatio="860" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1788" yWindow="576" windowWidth="19152" windowHeight="15636" tabRatio="860" firstSheet="6" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="151">
   <si>
     <t>對話內容</t>
   </si>
@@ -581,13 +580,17 @@
   </si>
   <si>
     <t>克拉拉工牌.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>露易絲錶通訊.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1578,18 +1581,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1612,7 +1615,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1666,15 +1669,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="122.125" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="122.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1697,7 +1700,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1720,7 +1723,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1743,7 +1746,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1774,17 +1777,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="35.875" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="35.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1807,7 +1810,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1830,7 +1833,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1860,14 +1863,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="81.125" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1890,7 +1893,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1920,14 +1923,14 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="183.75" customWidth="1"/>
+    <col min="3" max="3" width="183.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1950,7 +1953,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1973,7 +1976,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2003,15 +2006,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2034,7 +2037,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2057,7 +2060,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2087,22 +2090,22 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P62"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.5" customWidth="1"/>
-    <col min="3" max="3" width="90.375" customWidth="1"/>
-    <col min="4" max="4" width="16.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="90.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="12" max="12" width="22.5" customWidth="1"/>
-    <col min="15" max="15" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>67</v>
       </c>
@@ -2152,7 +2155,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2179,7 +2182,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2209,7 +2212,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="97.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2236,7 +2239,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2263,7 +2266,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2293,7 +2296,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2317,13 +2320,13 @@
         <v>12</v>
       </c>
       <c r="L7" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2347,10 +2350,10 @@
         <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2374,13 +2377,13 @@
         <v>12</v>
       </c>
       <c r="L9" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="P9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2404,10 +2407,10 @@
         <v>12</v>
       </c>
       <c r="L10" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2442,7 +2445,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2471,7 +2474,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2498,7 +2501,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2527,7 +2530,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2556,7 +2559,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2586,7 +2589,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2613,7 +2616,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2645,7 +2648,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2672,7 +2675,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2699,7 +2702,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2726,7 +2729,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2753,7 +2756,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2780,7 +2783,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2809,7 +2812,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2838,7 +2841,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2865,7 +2868,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2892,7 +2895,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2919,7 +2922,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2946,7 +2949,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2975,7 +2978,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3004,7 +3007,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3033,7 +3036,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3062,7 +3065,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3091,7 +3094,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3120,7 +3123,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3149,7 +3152,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3178,7 +3181,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3205,7 +3208,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3232,7 +3235,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3261,7 +3264,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3293,7 +3296,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3322,7 +3325,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3351,7 +3354,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3380,7 +3383,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3413,7 +3416,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3445,7 +3448,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3474,7 +3477,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3503,7 +3506,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3535,7 +3538,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3564,7 +3567,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3593,7 +3596,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3622,7 +3625,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3654,7 +3657,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3683,7 +3686,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3712,7 +3715,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3741,7 +3744,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3770,7 +3773,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3799,7 +3802,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3828,7 +3831,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3857,7 +3860,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3889,7 +3892,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>

--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C713DB09-6818-4C43-8336-59311278D2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1788" yWindow="576" windowWidth="19152" windowHeight="15636" tabRatio="860" firstSheet="6" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="860" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="150">
   <si>
     <t>對話內容</t>
   </si>
@@ -272,11 +273,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">淡入
-</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -436,161 +432,161 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>&lt;color=#61494E&gt;寂靜的回電過於嘮叨，她忍無可忍地停下通訊，修復後的通訊儀器猶如溺水者咳出肺泡中的鹹腥一般，不斷吐出低沉或是高亢的雜訊與音節。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;唯獨沒有：A13收到回覆，將立即派往支援......&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;來自17、18歲年輕女性，靦腆中又帶著敬重的語調，並非透過訊號傳遞，而是透過空氣中的震動，切實的扣嚮耳膜。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;她在撒謊，但現在還無人知道。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;黏膩的滑行聲又靠近了些，伴隨著一聲放心的嘆息。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;蛇？或是水管？&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;其實說是海洋軟體生物的腕足更貼切，青澀稚嫩的少女聲線出自一個非人形的智慧生命體。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;光滑的表皮上不只有黏液的透亮，兩顆荒誕到有點詭異的豆豆眼，被點在那個生物當作臉部的部位之上。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;詭異的令人發笑，細看甚至還有點可愛？&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;露易絲的嘴角抽搐了一剎，很快又歸於平靜。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;近距離觀察後，她保證不論兩顆小黑點的來源是什麼都不重要——它們的本質與初見的印象一般直白的荒唐，只是畫上去的，就像小孩子給氣球狗點睛。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;垂掛在充當脖頸處的曲折，是露易絲在企業最熟悉不過的物件──工牌。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;不似她在地球百科上見過的任何一種生物，反而更偏向某種劣質兒童玩具的存在又晃了晃身軀朝她更接近了些。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;助理：克拉拉。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;(......社區，在我來到這裡之後他們不只一次提過，雖然現在看不出來，但這裡以前是小有規模的聚落嗎？)&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;克拉拉頷首表示推理正確。露易絲不確定在襲擊事件發生後，她究竟走了多遠才抵達現在的落腳處，但14個日落的路程評估也是不少的距離。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;——襲擊事件的範圍比預想的大上不少，並不是特別針對他們外來者的攻擊，而是自然災害？&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;color=#61494E&gt;刺耳的廣播聲驟然響起，生生割裂了兩人的對話。&lt;/color&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉疑惑.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉疑惑dk.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景音樂</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>特效音</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>比較亮.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>小怪物監視器01.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>無線電雜音</t>
+  </si>
+  <si>
+    <t>黏液爬行聲</t>
+  </si>
+  <si>
+    <t>廣播提示音</t>
+  </si>
+  <si>
+    <t>電視旋鈕</t>
+  </si>
+  <si>
+    <t>Quiet_Days</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mercury_Fiction</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>無線電雜音2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>拍打</t>
+  </si>
+  <si>
+    <t>小怪物監視器01.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>小怪物水缸無手.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>小怪物水缸有手.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉眼.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>克拉拉工牌.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>露易絲錶通訊2.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>黑幕通訊.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;寂靜的回電過於嘮叨，她忍無可忍地停下通訊，修復後的通訊儀器猶如溺水者咳出肺泡中的鹹腥一般，不斷吐出低沉或是高亢的雜訊與音節。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;唯獨沒有：A13收到回覆，將立即派往支援......&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;來自17、18歲年輕女性，靦腆中又帶著敬重的語調，並非透過訊號傳遞，而是透過空氣中的震動，切實的扣嚮耳膜。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;她在撒謊，但現在還無人知道。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;黏膩的滑行聲又靠近了些，伴隨著一聲放心的嘆息。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;蛇？或是水管？&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;其實說是海洋軟體生物的腕足更貼切，青澀稚嫩的少女聲線出自一個非人形的智慧生命體。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;光滑的表皮上不只有黏液的透亮，兩顆荒誕到有點詭異的豆豆眼，被點在那個生物當作臉部的部位之上。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;詭異的令人發笑，細看甚至還有點可愛？&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;露易絲的嘴角抽搐了一剎，很快又歸於平靜。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;近距離觀察後，她保證不論兩顆小黑點的來源是什麼都不重要——它們的本質與初見的印象一般直白的荒唐，只是畫上去的，就像小孩子給氣球狗點睛。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;垂掛在充當脖頸處的曲折，是露易絲在企業最熟悉不過的物件──工牌。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;不似她在地球百科上見過的任何一種生物，反而更偏向某種劣質兒童玩具的存在又晃了晃身軀朝她更接近了些。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;助理：克拉拉。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;(......社區，在我來到這裡之後他們不只一次提過，雖然現在看不出來，但這裡以前是小有規模的聚落嗎？)&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;克拉拉頷首表示推理正確。露易絲不確定在襲擊事件發生後，她究竟走了多遠才抵達現在的落腳處，但14個日落的路程評估也是不少的距離。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;——襲擊事件的範圍比預想的大上不少，並不是特別針對他們外來者的攻擊，而是自然災害？&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;color=#61494E&gt;刺耳的廣播聲驟然響起，生生割裂了兩人的對話。&lt;/color&gt;</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉疑惑.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉疑惑dk.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景音樂</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>特效音</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>比較亮.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>小怪物監視器01.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>無線電雜音</t>
-  </si>
-  <si>
-    <t>黏液爬行聲</t>
-  </si>
-  <si>
-    <t>廣播提示音</t>
-  </si>
-  <si>
-    <t>電視旋鈕</t>
-  </si>
-  <si>
-    <t>Quiet_Days</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mercury_Fiction</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>無線電雜音2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>拍打</t>
-  </si>
-  <si>
-    <t>小怪物監視器01.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>小怪物水缸無手.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>小怪物水缸有手.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉眼.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>克拉拉工牌.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>露易絲錶通訊.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1581,18 +1577,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1615,7 +1611,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1638,7 +1634,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1669,15 +1665,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="3" max="3" width="122.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="3" max="3" width="122.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1700,7 +1696,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1723,7 +1719,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1746,7 +1742,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1777,17 +1773,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="35.88671875" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="1" max="1" width="5.125" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="35.875" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1810,7 +1806,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="48.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1833,7 +1829,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1863,14 +1859,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="81.109375" customWidth="1"/>
+    <col min="3" max="3" width="81.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1893,7 +1889,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1923,14 +1919,14 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="183.77734375" customWidth="1"/>
+    <col min="3" max="3" width="183.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1953,7 +1949,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1976,7 +1972,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2006,15 +2002,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2037,7 +2033,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2060,7 +2056,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2090,22 +2086,22 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:P62"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
-    <col min="3" max="3" width="90.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="29.5" customWidth="1"/>
+    <col min="3" max="3" width="90.375" customWidth="1"/>
+    <col min="4" max="4" width="16.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="12" max="12" width="22.44140625" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.5" customWidth="1"/>
+    <col min="15" max="15" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>67</v>
       </c>
@@ -2116,52 +2112,52 @@
         <v>0</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="F1" t="s">
         <v>69</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="J1" t="s">
         <v>68</v>
       </c>
       <c r="K1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" t="s">
         <v>85</v>
       </c>
-      <c r="L1" t="s">
-        <v>86</v>
-      </c>
       <c r="M1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -2173,22 +2169,22 @@
         <v>51</v>
       </c>
       <c r="J2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K2" t="s">
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -2200,25 +2196,25 @@
         <v>51</v>
       </c>
       <c r="J3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
       </c>
       <c r="L3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="97.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -2236,16 +2232,16 @@
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -2257,46 +2253,46 @@
         <v>51</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K5" t="s">
         <v>12</v>
       </c>
       <c r="L5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" t="s">
         <v>110</v>
       </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" t="s">
-        <v>111</v>
-      </c>
       <c r="P6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2314,19 +2310,19 @@
         <v>51</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K7" t="s">
         <v>12</v>
       </c>
       <c r="L7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2344,22 +2340,22 @@
         <v>51</v>
       </c>
       <c r="J8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K8" t="s">
         <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -2371,25 +2367,25 @@
         <v>51</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K9" t="s">
         <v>12</v>
       </c>
       <c r="L9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="P9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -2398,19 +2394,19 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s">
         <v>12</v>
       </c>
       <c r="L10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2421,31 +2417,34 @@
         <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" t="s">
         <v>72</v>
       </c>
-      <c r="J11" t="s">
-        <v>73</v>
-      </c>
       <c r="K11" t="s">
         <v>12</v>
       </c>
       <c r="L11" t="s">
-        <v>135</v>
+        <v>133</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="O11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="P11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2456,52 +2455,52 @@
         <v>14</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F12" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s">
         <v>72</v>
       </c>
-      <c r="J12" t="s">
-        <v>73</v>
-      </c>
       <c r="K12" t="s">
         <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" t="s">
         <v>72</v>
       </c>
-      <c r="J13" t="s">
-        <v>73</v>
-      </c>
       <c r="K13" t="s">
         <v>12</v>
       </c>
       <c r="L13" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2512,96 +2511,96 @@
         <v>16</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" t="s">
         <v>72</v>
       </c>
-      <c r="J14" t="s">
-        <v>73</v>
-      </c>
       <c r="K14" t="s">
         <v>12</v>
       </c>
       <c r="L14" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F15" t="s">
         <v>51</v>
       </c>
       <c r="J15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K15" t="s">
         <v>12</v>
       </c>
       <c r="L15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F16" t="s">
         <v>51</v>
       </c>
       <c r="J16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" t="s">
+        <v>133</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="K16" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" t="s">
-        <v>135</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
         <v>51</v>
@@ -2613,10 +2612,10 @@
         <v>12</v>
       </c>
       <c r="L17" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2624,13 +2623,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F18" t="s">
         <v>51</v>
@@ -2642,25 +2641,25 @@
         <v>12</v>
       </c>
       <c r="L18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" t="s">
         <v>51</v>
@@ -2672,49 +2671,49 @@
         <v>12</v>
       </c>
       <c r="L19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F20" t="s">
         <v>51</v>
       </c>
       <c r="J20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K20" t="s">
         <v>12</v>
       </c>
       <c r="L20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
         <v>51</v>
@@ -2726,49 +2725,49 @@
         <v>12</v>
       </c>
       <c r="L21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F22" t="s">
         <v>51</v>
       </c>
       <c r="J22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K22" t="s">
         <v>12</v>
       </c>
       <c r="L22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F23" t="s">
         <v>51</v>
@@ -2780,53 +2779,53 @@
         <v>12</v>
       </c>
       <c r="L23" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="F24" t="s">
         <v>51</v>
       </c>
       <c r="J24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K24" t="s">
         <v>12</v>
       </c>
       <c r="L24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="F25" t="s">
         <v>51</v>
@@ -2838,16 +2837,16 @@
         <v>12</v>
       </c>
       <c r="L25" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
         <v>12</v>
@@ -2865,16 +2864,16 @@
         <v>12</v>
       </c>
       <c r="L26" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
         <v>12</v>
@@ -2886,22 +2885,22 @@
         <v>51</v>
       </c>
       <c r="J27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K27" t="s">
         <v>12</v>
       </c>
       <c r="L27" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
         <v>12</v>
@@ -2913,22 +2912,22 @@
         <v>51</v>
       </c>
       <c r="J28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K28" t="s">
         <v>12</v>
       </c>
       <c r="L28" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
         <v>12</v>
@@ -2940,30 +2939,30 @@
         <v>51</v>
       </c>
       <c r="J29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K29" t="s">
         <v>12</v>
       </c>
       <c r="L29" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F30" t="s">
         <v>51</v>
@@ -2975,24 +2974,24 @@
         <v>12</v>
       </c>
       <c r="L30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F31" t="s">
         <v>51</v>
@@ -3004,111 +3003,111 @@
         <v>12</v>
       </c>
       <c r="L31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="33" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F32" t="s">
         <v>51</v>
       </c>
       <c r="J32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K32" t="s">
         <v>12</v>
       </c>
       <c r="L32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="F33" t="s">
         <v>51</v>
       </c>
       <c r="J33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s">
         <v>12</v>
       </c>
       <c r="L33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F34" t="s">
         <v>51</v>
       </c>
       <c r="J34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K34" t="s">
         <v>12</v>
       </c>
       <c r="L34" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F35" t="s">
         <v>51</v>
@@ -3120,24 +3119,24 @@
         <v>12</v>
       </c>
       <c r="L35" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F36" t="s">
         <v>51</v>
@@ -3149,78 +3148,78 @@
         <v>12</v>
       </c>
       <c r="L36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F37" t="s">
         <v>51</v>
       </c>
       <c r="J37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K37" t="s">
         <v>12</v>
       </c>
       <c r="L37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F38" t="s">
         <v>51</v>
       </c>
       <c r="J38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K38" t="s">
         <v>12</v>
       </c>
       <c r="L38" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="33" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F39" t="s">
         <v>51</v>
@@ -3232,24 +3231,24 @@
         <v>12</v>
       </c>
       <c r="L39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>51</v>
@@ -3261,114 +3260,114 @@
         <v>12</v>
       </c>
       <c r="L40" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F41" t="s">
         <v>51</v>
       </c>
       <c r="J41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K41" t="s">
         <v>12</v>
       </c>
       <c r="L41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N41" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
         <v>51</v>
       </c>
       <c r="J42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K42" t="s">
         <v>12</v>
       </c>
       <c r="L42" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F43" t="s">
         <v>51</v>
       </c>
       <c r="J43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K43" t="s">
         <v>12</v>
       </c>
       <c r="L43" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F44" t="s">
         <v>51</v>
@@ -3380,57 +3379,57 @@
         <v>12</v>
       </c>
       <c r="L44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F45" t="s">
         <v>51</v>
       </c>
       <c r="J45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K45" t="s">
         <v>12</v>
       </c>
       <c r="L45" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P45" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D46" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" t="s">
-        <v>12</v>
+      <c r="D46" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="F46" t="s">
         <v>51</v>
@@ -3442,71 +3441,71 @@
         <v>12</v>
       </c>
       <c r="L46" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="N46" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" t="s">
-        <v>12</v>
+      <c r="D47" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="F47" t="s">
         <v>51</v>
       </c>
       <c r="J47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K47" t="s">
         <v>12</v>
       </c>
       <c r="L47" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D48" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" t="s">
-        <v>12</v>
+      <c r="D48" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="F48" t="s">
         <v>51</v>
       </c>
       <c r="J48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K48" t="s">
         <v>12</v>
       </c>
       <c r="L48" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3526,19 +3525,22 @@
         <v>51</v>
       </c>
       <c r="J49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K49" t="s">
         <v>12</v>
       </c>
       <c r="L49" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="N49" t="s">
+        <v>78</v>
       </c>
       <c r="P49" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3558,16 +3560,16 @@
         <v>51</v>
       </c>
       <c r="J50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K50" t="s">
         <v>12</v>
       </c>
       <c r="L50" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3587,16 +3589,16 @@
         <v>51</v>
       </c>
       <c r="J51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K51" t="s">
         <v>12</v>
       </c>
       <c r="L51" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3616,16 +3618,16 @@
         <v>51</v>
       </c>
       <c r="J52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K52" t="s">
         <v>12</v>
       </c>
       <c r="L52" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3645,19 +3647,16 @@
         <v>51</v>
       </c>
       <c r="J53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K53" t="s">
         <v>12</v>
       </c>
       <c r="L53" t="s">
-        <v>136</v>
-      </c>
-      <c r="N53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3683,10 +3682,13 @@
         <v>12</v>
       </c>
       <c r="L54" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="N54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3712,10 +3714,10 @@
         <v>12</v>
       </c>
       <c r="L55" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3741,10 +3743,10 @@
         <v>12</v>
       </c>
       <c r="L56" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3770,10 +3772,10 @@
         <v>12</v>
       </c>
       <c r="L57" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3799,10 +3801,10 @@
         <v>12</v>
       </c>
       <c r="L58" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3828,10 +3830,10 @@
         <v>12</v>
       </c>
       <c r="L59" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3857,10 +3859,10 @@
         <v>12</v>
       </c>
       <c r="L60" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3886,13 +3888,13 @@
         <v>12</v>
       </c>
       <c r="L61" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P61" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3918,10 +3920,10 @@
         <v>12</v>
       </c>
       <c r="L62" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="P62" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Story.xlsx
+++ b/Assets/StreamingAssets/Story.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linsa\Documents\GitHub\LivingInTheRuins\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C713DB09-6818-4C43-8336-59311278D2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="860" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="860" firstSheet="6" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="第一個說明對話" sheetId="1" r:id="rId1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="149">
   <si>
     <t>對話內容</t>
   </si>
@@ -553,10 +552,6 @@
   </si>
   <si>
     <t>拍打</t>
-  </si>
-  <si>
-    <t>小怪物監視器01.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>小怪物水缸無手.png</t>
@@ -586,7 +581,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1577,18 +1572,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1611,7 +1606,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1634,7 +1629,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1665,15 +1660,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="23.875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="23.88671875" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.375" customWidth="1"/>
-    <col min="3" max="3" width="122.125" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="3" max="3" width="122.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1696,7 +1691,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1719,7 +1714,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1742,7 +1737,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1773,17 +1768,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="35.875" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="35.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1806,7 +1801,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1829,7 +1824,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1859,14 +1854,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="81.125" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1889,7 +1884,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1919,14 +1914,14 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="183.75" customWidth="1"/>
+    <col min="3" max="3" width="183.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1949,7 +1944,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1972,7 +1967,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2002,15 +1997,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2033,7 +2028,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2056,7 +2051,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2086,22 +2081,22 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P62"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.5" customWidth="1"/>
-    <col min="3" max="3" width="90.375" customWidth="1"/>
-    <col min="4" max="4" width="16.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="90.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="12" max="12" width="22.5" customWidth="1"/>
-    <col min="15" max="15" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>67</v>
       </c>
@@ -2151,7 +2146,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2178,7 +2173,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2208,7 +2203,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="97.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="97.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2235,7 +2230,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2262,7 +2257,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2292,7 +2287,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2313,16 +2308,16 @@
         <v>72</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="L7" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2343,13 +2338,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="L8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2370,16 +2365,16 @@
         <v>72</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="L9" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="P9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2400,13 +2395,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2444,7 +2439,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2473,7 +2468,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2500,7 +2495,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2529,7 +2524,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2558,7 +2553,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2588,7 +2583,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2615,7 +2610,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2647,7 +2642,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2674,7 +2669,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2701,7 +2696,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2728,7 +2723,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2755,7 +2750,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2782,7 +2777,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2811,7 +2806,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2840,7 +2835,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2861,13 +2856,13 @@
         <v>5</v>
       </c>
       <c r="K26" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="L26" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2888,13 +2883,13 @@
         <v>74</v>
       </c>
       <c r="K27" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="L27" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2915,13 +2910,13 @@
         <v>75</v>
       </c>
       <c r="K28" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="L28" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2942,13 +2937,13 @@
         <v>76</v>
       </c>
       <c r="K29" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="L29" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2977,7 +2972,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3006,7 +3001,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3035,7 +3030,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3064,7 +3059,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3093,7 +3088,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3122,7 +3117,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3151,7 +3146,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3180,7 +3175,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3207,7 +3202,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3234,7 +3229,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3263,7 +3258,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3295,7 +3290,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3324,7 +3319,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3353,7 +3348,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3382,7 +3377,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3415,7 +3410,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3441,13 +3436,13 @@
         <v>12</v>
       </c>
       <c r="L46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N46" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3473,10 +3468,10 @@
         <v>12</v>
       </c>
       <c r="L47" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3502,10 +3497,10 @@
         <v>12</v>
       </c>
       <c r="L48" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3528,10 +3523,10 @@
         <v>72</v>
       </c>
       <c r="K49" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="L49" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="N49" t="s">
         <v>78</v>
@@ -3540,7 +3535,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3563,13 +3558,13 @@
         <v>72</v>
       </c>
       <c r="K50" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3592,13 +3587,13 @@
         <v>72</v>
       </c>
       <c r="K51" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="L51" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3621,13 +3616,13 @@
         <v>74</v>
       </c>
       <c r="K52" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="L52" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3650,13 +3645,13 @@
         <v>72</v>
       </c>
       <c r="K53" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="L53" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3679,16 +3674,16 @@
         <v>5</v>
       </c>
       <c r="K54" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="L54" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="N54" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3711,13 +3706,13 @@
         <v>5</v>
       </c>
       <c r="K55" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="L55" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3740,13 +3735,13 @@
         <v>5</v>
       </c>
       <c r="K56" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="L56" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3769,13 +3764,13 @@
         <v>5</v>
       </c>
       <c r="K57" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="L57" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3798,13 +3793,13 @@
         <v>5</v>
       </c>
       <c r="K58" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="L58" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3827,13 +3822,13 @@
         <v>5</v>
       </c>
       <c r="K59" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="L59" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3856,13 +3851,13 @@
         <v>5</v>
       </c>
       <c r="K60" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="L60" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3885,16 +3880,16 @@
         <v>5</v>
       </c>
       <c r="K61" t="s">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="L61" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P61" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3917,10 +3912,10 @@
         <v>5</v>
       </c>
       <c r="K62" t="s">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="L62" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P62" t="s">
         <v>142</v>
